--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,126 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125899057</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kurlberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>516357</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6691373</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Under äldre tall på myrstacken under trädet.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Kjell-Åke Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,2302 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125404325</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kurlberget, Kurlberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516444</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6691419</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125402480</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516445</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6691532</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125402947</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516437</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6691535</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125404723</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516359</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6691288</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125406131</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516270</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6691537</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125401494</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516605</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6691608</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125404849</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516345</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6691330</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125407168</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516431</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6691633</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125406787</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516368</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6691594</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125406595</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516329</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6691615</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125408185</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516621</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6691733</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125402537</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516437</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6691550</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125401741</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516551</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6691659</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125408231</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516621</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6691736</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125404817</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516346</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6691330</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125402359</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516433</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6691624</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125408367</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516605</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6691759</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125405426</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516386</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6691468</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125404419</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516440</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6691418</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125404997</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>516353</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6691382</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125404275</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>516445</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6691423</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125406873</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>516372</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6691600</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125401530</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>516605</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6691608</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125402480</v>
+        <v>125402947</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>97212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,42 +1010,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516445</v>
+        <v>516437</v>
       </c>
       <c r="R5" t="n">
-        <v>6691532</v>
+        <v>6691535</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125402947</v>
+        <v>125402480</v>
       </c>
       <c r="B6" t="n">
-        <v>97212</v>
+        <v>56843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,37 +1107,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516437</v>
+        <v>516445</v>
       </c>
       <c r="R6" t="n">
-        <v>6691535</v>
+        <v>6691532</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1407,48 +1407,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>56834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R9" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,53 +1509,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>56834</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R10" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>97212</v>
+        <v>56843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,34 +2908,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R24" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>97212</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3010,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R25" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,39 +3107,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R26" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125402947</v>
+        <v>125402480</v>
       </c>
       <c r="B5" t="n">
-        <v>97212</v>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,37 +1010,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516437</v>
+        <v>516445</v>
       </c>
       <c r="R5" t="n">
-        <v>6691535</v>
+        <v>6691532</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125402480</v>
+        <v>125402947</v>
       </c>
       <c r="B6" t="n">
-        <v>56843</v>
+        <v>97213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,42 +1112,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516445</v>
+        <v>516437</v>
       </c>
       <c r="R6" t="n">
-        <v>6691532</v>
+        <v>6691535</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>125406595</v>
       </c>
       <c r="B13" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>125408185</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>125408231</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>125408367</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>125405426</v>
       </c>
       <c r="B21" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125401530</v>
+        <v>125404275</v>
       </c>
       <c r="B24" t="n">
-        <v>56843</v>
+        <v>97213</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,39 +2908,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516605</v>
+        <v>516445</v>
       </c>
       <c r="R24" t="n">
-        <v>6691608</v>
+        <v>6691423</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125404275</v>
+        <v>125406873</v>
       </c>
       <c r="B25" t="n">
-        <v>97212</v>
+        <v>98353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3034,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516445</v>
+        <v>516372</v>
       </c>
       <c r="R25" t="n">
-        <v>6691423</v>
+        <v>6691600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125406873</v>
+        <v>125401530</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>56843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,34 +3102,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516372</v>
+        <v>516605</v>
       </c>
       <c r="R26" t="n">
-        <v>6691600</v>
+        <v>6691608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -1104,7 +1104,7 @@
         <v>125402947</v>
       </c>
       <c r="B6" t="n">
-        <v>97213</v>
+        <v>97215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,53 +1407,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B9" t="n">
-        <v>56834</v>
+        <v>98355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R9" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,48 +1504,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B10" t="n">
-        <v>98353</v>
+        <v>56834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R10" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125406595</v>
+        <v>125408185</v>
       </c>
       <c r="B13" t="n">
-        <v>98332</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516329</v>
+        <v>516621</v>
       </c>
       <c r="R13" t="n">
-        <v>6691615</v>
+        <v>6691733</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,45 +1902,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408185</v>
+        <v>125402537</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516621</v>
+        <v>516437</v>
       </c>
       <c r="R14" t="n">
-        <v>6691733</v>
+        <v>6691550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,53 +2004,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125402537</v>
+        <v>125406595</v>
       </c>
       <c r="B15" t="n">
-        <v>56843</v>
+        <v>98334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516437</v>
+        <v>516329</v>
       </c>
       <c r="R15" t="n">
-        <v>6691550</v>
+        <v>6691615</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>125405426</v>
       </c>
       <c r="B21" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>97213</v>
+        <v>56843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,34 +2908,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R24" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>98353</v>
+        <v>97215</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3010,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R25" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>98355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,39 +3107,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R26" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -2596,48 +2596,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B21" t="n">
-        <v>98334</v>
+        <v>56843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R21" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,53 +2698,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B22" t="n">
-        <v>56843</v>
+        <v>98334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R22" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B24" t="n">
-        <v>56843</v>
+        <v>98355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,39 +2908,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R24" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B25" t="n">
-        <v>97215</v>
+        <v>56843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,34 +3005,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R25" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>97215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R26" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -897,50 +897,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125404325</v>
+        <v>125402480</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516444</v>
+        <v>516445</v>
       </c>
       <c r="R4" t="n">
-        <v>6691419</v>
+        <v>6691532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,50 +999,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125402480</v>
+        <v>125404325</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>57648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516445</v>
+        <v>516444</v>
       </c>
       <c r="R5" t="n">
-        <v>6691532</v>
+        <v>6691419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
         <v>125402947</v>
       </c>
       <c r="B6" t="n">
-        <v>97215</v>
+        <v>97219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>125401494</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,45 +1805,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125408185</v>
+        <v>125402537</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>56843</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516621</v>
+        <v>516437</v>
       </c>
       <c r="R13" t="n">
-        <v>6691733</v>
+        <v>6691550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,50 +1907,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125402537</v>
+        <v>125408185</v>
       </c>
       <c r="B14" t="n">
-        <v>56843</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516437</v>
+        <v>516621</v>
       </c>
       <c r="R14" t="n">
-        <v>6691550</v>
+        <v>6691733</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
         <v>125406595</v>
       </c>
       <c r="B15" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>125408231</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>125408367</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>125405426</v>
       </c>
       <c r="B22" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>97219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R24" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B25" t="n">
-        <v>56843</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,39 +3005,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R25" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B26" t="n">
-        <v>97215</v>
+        <v>56843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,34 +3102,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R26" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>97219</v>
+        <v>56843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,34 +2908,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R24" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>97219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3010,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R25" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>56843</v>
+        <v>98359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,39 +3107,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R26" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -897,50 +897,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125402480</v>
+        <v>125404325</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516445</v>
+        <v>516444</v>
       </c>
       <c r="R4" t="n">
-        <v>6691532</v>
+        <v>6691419</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,50 +999,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125404325</v>
+        <v>125402480</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516444</v>
+        <v>516445</v>
       </c>
       <c r="R5" t="n">
-        <v>6691419</v>
+        <v>6691532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
         <v>125402947</v>
       </c>
       <c r="B6" t="n">
-        <v>97219</v>
+        <v>97220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,48 +1407,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B9" t="n">
-        <v>98359</v>
+        <v>56834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R9" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,53 +1509,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>56834</v>
+        <v>98360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R10" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,53 +1805,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125402537</v>
+        <v>125406595</v>
       </c>
       <c r="B13" t="n">
-        <v>56843</v>
+        <v>98339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516437</v>
+        <v>516329</v>
       </c>
       <c r="R13" t="n">
-        <v>6691550</v>
+        <v>6691615</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,48 +1999,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125406595</v>
+        <v>125402537</v>
       </c>
       <c r="B15" t="n">
-        <v>98338</v>
+        <v>56843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516329</v>
+        <v>516437</v>
       </c>
       <c r="R15" t="n">
-        <v>6691615</v>
+        <v>6691550</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2596,53 +2596,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B21" t="n">
-        <v>56843</v>
+        <v>98339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R21" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2698,48 +2693,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B22" t="n">
-        <v>98338</v>
+        <v>56843</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R22" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>97219</v>
+        <v>97220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -2596,48 +2596,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B21" t="n">
-        <v>98339</v>
+        <v>56843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R21" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,53 +2698,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B22" t="n">
-        <v>56843</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R22" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125899057</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,53 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125404325</v>
+        <v>125402947</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>97222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516444</v>
+        <v>516437</v>
       </c>
       <c r="R4" t="n">
-        <v>6691419</v>
+        <v>6691535</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,50 +994,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125402480</v>
+        <v>125404325</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>57649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516445</v>
+        <v>516444</v>
       </c>
       <c r="R5" t="n">
-        <v>6691532</v>
+        <v>6691419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125402947</v>
+        <v>125402480</v>
       </c>
       <c r="B6" t="n">
-        <v>97220</v>
+        <v>56844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,37 +1107,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516437</v>
+        <v>516445</v>
       </c>
       <c r="R6" t="n">
-        <v>6691535</v>
+        <v>6691532</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>125404723</v>
       </c>
       <c r="B7" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,53 +1407,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B9" t="n">
-        <v>56834</v>
+        <v>98362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R9" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,48 +1504,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B10" t="n">
-        <v>98360</v>
+        <v>56835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R10" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>125407168</v>
       </c>
       <c r="B11" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,48 +1805,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125406595</v>
+        <v>125402537</v>
       </c>
       <c r="B13" t="n">
-        <v>98339</v>
+        <v>56844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516329</v>
+        <v>516437</v>
       </c>
       <c r="R13" t="n">
-        <v>6691615</v>
+        <v>6691550</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,32 +1907,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408185</v>
+        <v>125406595</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,13 +1942,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516621</v>
+        <v>516329</v>
       </c>
       <c r="R14" t="n">
-        <v>6691733</v>
+        <v>6691615</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1999,50 +2004,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125402537</v>
+        <v>125408185</v>
       </c>
       <c r="B15" t="n">
-        <v>56843</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516437</v>
+        <v>516621</v>
       </c>
       <c r="R15" t="n">
-        <v>6691550</v>
+        <v>6691733</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,7 +2104,7 @@
         <v>125401741</v>
       </c>
       <c r="B16" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>125408231</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>125402359</v>
       </c>
       <c r="B19" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>125408367</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,53 +2596,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B21" t="n">
-        <v>56843</v>
+        <v>98341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R21" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2698,48 +2693,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>56844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R22" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>125404997</v>
       </c>
       <c r="B23" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>97220</v>
+        <v>97222</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -2596,48 +2596,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B21" t="n">
-        <v>98341</v>
+        <v>56844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R21" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,53 +2698,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B22" t="n">
-        <v>56844</v>
+        <v>98341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R22" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -897,48 +897,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125402947</v>
+        <v>125404325</v>
       </c>
       <c r="B4" t="n">
-        <v>97222</v>
+        <v>57649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516437</v>
+        <v>516444</v>
       </c>
       <c r="R4" t="n">
-        <v>6691535</v>
+        <v>6691419</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,50 +999,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125404325</v>
+        <v>125402480</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>56844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516444</v>
+        <v>516445</v>
       </c>
       <c r="R5" t="n">
-        <v>6691419</v>
+        <v>6691532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125402480</v>
+        <v>125402947</v>
       </c>
       <c r="B6" t="n">
-        <v>56844</v>
+        <v>97224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,42 +1112,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516445</v>
+        <v>516437</v>
       </c>
       <c r="R6" t="n">
-        <v>6691532</v>
+        <v>6691535</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>125401494</v>
       </c>
       <c r="B9" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,50 +1805,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125402537</v>
+        <v>125408185</v>
       </c>
       <c r="B13" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516437</v>
+        <v>516621</v>
       </c>
       <c r="R13" t="n">
-        <v>6691550</v>
+        <v>6691733</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,48 +1902,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125406595</v>
+        <v>125402537</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>56844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516329</v>
+        <v>516437</v>
       </c>
       <c r="R14" t="n">
-        <v>6691615</v>
+        <v>6691550</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2004,32 +2004,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125408185</v>
+        <v>125406595</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516621</v>
+        <v>516329</v>
       </c>
       <c r="R15" t="n">
-        <v>6691733</v>
+        <v>6691615</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>125405426</v>
       </c>
       <c r="B22" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125401530</v>
+        <v>125404275</v>
       </c>
       <c r="B24" t="n">
-        <v>56844</v>
+        <v>97224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,39 +2908,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516605</v>
+        <v>516445</v>
       </c>
       <c r="R24" t="n">
-        <v>6691608</v>
+        <v>6691423</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125404275</v>
+        <v>125406873</v>
       </c>
       <c r="B25" t="n">
-        <v>97222</v>
+        <v>98364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3034,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516445</v>
+        <v>516372</v>
       </c>
       <c r="R25" t="n">
-        <v>6691423</v>
+        <v>6691600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125406873</v>
+        <v>125401530</v>
       </c>
       <c r="B26" t="n">
-        <v>98362</v>
+        <v>56844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,34 +3102,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516372</v>
+        <v>516605</v>
       </c>
       <c r="R26" t="n">
-        <v>6691600</v>
+        <v>6691608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125408185</v>
+        <v>125406595</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516621</v>
+        <v>516329</v>
       </c>
       <c r="R13" t="n">
-        <v>6691733</v>
+        <v>6691615</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,50 +1902,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125402537</v>
+        <v>125408185</v>
       </c>
       <c r="B14" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516437</v>
+        <v>516621</v>
       </c>
       <c r="R14" t="n">
-        <v>6691550</v>
+        <v>6691733</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,48 +1999,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125406595</v>
+        <v>125402537</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>56844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516329</v>
+        <v>516437</v>
       </c>
       <c r="R15" t="n">
-        <v>6691615</v>
+        <v>6691550</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2596,53 +2596,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B21" t="n">
-        <v>56844</v>
+        <v>98343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R21" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2698,48 +2693,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>56844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R22" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>97224</v>
+        <v>56844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,34 +2908,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R24" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>98364</v>
+        <v>97224</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3010,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R25" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>56844</v>
+        <v>98364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,39 +3107,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R26" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -1104,7 +1104,7 @@
         <v>125402947</v>
       </c>
       <c r="B6" t="n">
-        <v>97224</v>
+        <v>97226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,48 +1407,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>56835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R9" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,53 +1509,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>56835</v>
+        <v>98366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R10" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125406595</v>
+        <v>125408185</v>
       </c>
       <c r="B13" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516329</v>
+        <v>516621</v>
       </c>
       <c r="R13" t="n">
-        <v>6691615</v>
+        <v>6691733</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,45 +1902,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408185</v>
+        <v>125402537</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516621</v>
+        <v>516437</v>
       </c>
       <c r="R14" t="n">
-        <v>6691733</v>
+        <v>6691550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,53 +2004,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125402537</v>
+        <v>125406595</v>
       </c>
       <c r="B15" t="n">
-        <v>56844</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516437</v>
+        <v>516329</v>
       </c>
       <c r="R15" t="n">
-        <v>6691550</v>
+        <v>6691615</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>125405426</v>
       </c>
       <c r="B21" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>97224</v>
+        <v>97226</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125899057</v>
       </c>
       <c r="B3" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,53 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125404325</v>
+        <v>125402947</v>
       </c>
       <c r="B4" t="n">
-        <v>57649</v>
+        <v>97230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516444</v>
+        <v>516437</v>
       </c>
       <c r="R4" t="n">
-        <v>6691419</v>
+        <v>6691535</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,50 +994,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125402480</v>
+        <v>125404325</v>
       </c>
       <c r="B5" t="n">
-        <v>56844</v>
+        <v>57653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516445</v>
+        <v>516444</v>
       </c>
       <c r="R5" t="n">
-        <v>6691532</v>
+        <v>6691419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125402947</v>
+        <v>125402480</v>
       </c>
       <c r="B6" t="n">
-        <v>97226</v>
+        <v>56848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,37 +1107,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516437</v>
+        <v>516445</v>
       </c>
       <c r="R6" t="n">
-        <v>6691535</v>
+        <v>6691532</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>125404723</v>
       </c>
       <c r="B7" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>125404849</v>
       </c>
       <c r="B9" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>125407168</v>
       </c>
       <c r="B11" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,45 +1805,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125408185</v>
+        <v>125402537</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>56848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516621</v>
+        <v>516437</v>
       </c>
       <c r="R13" t="n">
-        <v>6691733</v>
+        <v>6691550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,50 +1907,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125402537</v>
+        <v>125408185</v>
       </c>
       <c r="B14" t="n">
-        <v>56844</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516437</v>
+        <v>516621</v>
       </c>
       <c r="R14" t="n">
-        <v>6691550</v>
+        <v>6691733</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
         <v>125406595</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>125401741</v>
       </c>
       <c r="B16" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>125408231</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>125402359</v>
       </c>
       <c r="B19" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>125408367</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,48 +2596,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B21" t="n">
-        <v>98345</v>
+        <v>56848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R21" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,53 +2698,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B22" t="n">
-        <v>56844</v>
+        <v>98349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R22" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>125404997</v>
       </c>
       <c r="B23" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>97226</v>
+        <v>97230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125402947</v>
+        <v>125402480</v>
       </c>
       <c r="B4" t="n">
-        <v>97230</v>
+        <v>56848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,37 +908,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516437</v>
+        <v>516445</v>
       </c>
       <c r="R4" t="n">
-        <v>6691535</v>
+        <v>6691532</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1096,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125402480</v>
+        <v>125402947</v>
       </c>
       <c r="B6" t="n">
-        <v>56848</v>
+        <v>97230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,42 +1112,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516445</v>
+        <v>516437</v>
       </c>
       <c r="R6" t="n">
-        <v>6691532</v>
+        <v>6691535</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125401530</v>
+        <v>125404275</v>
       </c>
       <c r="B24" t="n">
-        <v>56848</v>
+        <v>97230</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,39 +2908,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516605</v>
+        <v>516445</v>
       </c>
       <c r="R24" t="n">
-        <v>6691608</v>
+        <v>6691423</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125404275</v>
+        <v>125406873</v>
       </c>
       <c r="B25" t="n">
-        <v>97230</v>
+        <v>98370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3034,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516445</v>
+        <v>516372</v>
       </c>
       <c r="R25" t="n">
-        <v>6691423</v>
+        <v>6691600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125406873</v>
+        <v>125401530</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>56848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,34 +3102,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516372</v>
+        <v>516605</v>
       </c>
       <c r="R26" t="n">
-        <v>6691600</v>
+        <v>6691608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -897,50 +897,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125402480</v>
+        <v>125404325</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>57653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516445</v>
+        <v>516444</v>
       </c>
       <c r="R4" t="n">
-        <v>6691532</v>
+        <v>6691419</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,50 +999,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125404325</v>
+        <v>125402480</v>
       </c>
       <c r="B5" t="n">
-        <v>57653</v>
+        <v>56848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516444</v>
+        <v>516445</v>
       </c>
       <c r="R5" t="n">
-        <v>6691419</v>
+        <v>6691532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
         <v>125402947</v>
       </c>
       <c r="B6" t="n">
-        <v>97230</v>
+        <v>97233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,53 +1805,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125402537</v>
+        <v>125406595</v>
       </c>
       <c r="B13" t="n">
-        <v>56848</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516437</v>
+        <v>516329</v>
       </c>
       <c r="R13" t="n">
-        <v>6691550</v>
+        <v>6691615</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,48 +1999,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125406595</v>
+        <v>125402537</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>56848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516329</v>
+        <v>516437</v>
       </c>
       <c r="R15" t="n">
-        <v>6691615</v>
+        <v>6691550</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2596,53 +2596,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B21" t="n">
-        <v>56848</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R21" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2698,48 +2693,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B22" t="n">
-        <v>98349</v>
+        <v>56848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R22" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>97230</v>
+        <v>56848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,34 +2908,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R24" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>97233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3010,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R25" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>56848</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,39 +3107,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R26" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -1407,53 +1407,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B9" t="n">
-        <v>56839</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R9" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,48 +1504,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B10" t="n">
-        <v>98373</v>
+        <v>56839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R10" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125406595</v>
+        <v>125408185</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516329</v>
+        <v>516621</v>
       </c>
       <c r="R13" t="n">
-        <v>6691615</v>
+        <v>6691733</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,45 +1902,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408185</v>
+        <v>125402537</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516621</v>
+        <v>516437</v>
       </c>
       <c r="R14" t="n">
-        <v>6691733</v>
+        <v>6691550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,53 +2004,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125402537</v>
+        <v>125406595</v>
       </c>
       <c r="B15" t="n">
-        <v>56848</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516437</v>
+        <v>516329</v>
       </c>
       <c r="R15" t="n">
-        <v>6691550</v>
+        <v>6691615</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125401530</v>
+        <v>125404275</v>
       </c>
       <c r="B24" t="n">
-        <v>56848</v>
+        <v>97233</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,39 +2908,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516605</v>
+        <v>516445</v>
       </c>
       <c r="R24" t="n">
-        <v>6691608</v>
+        <v>6691423</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125404275</v>
+        <v>125406873</v>
       </c>
       <c r="B25" t="n">
-        <v>97233</v>
+        <v>98373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3034,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516445</v>
+        <v>516372</v>
       </c>
       <c r="R25" t="n">
-        <v>6691423</v>
+        <v>6691600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125406873</v>
+        <v>125401530</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>56848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,34 +3102,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516372</v>
+        <v>516605</v>
       </c>
       <c r="R26" t="n">
-        <v>6691600</v>
+        <v>6691608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -1407,48 +1407,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>56839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R9" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,53 +1509,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>56839</v>
+        <v>98373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R10" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125408185</v>
+        <v>125406595</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516621</v>
+        <v>516329</v>
       </c>
       <c r="R13" t="n">
-        <v>6691733</v>
+        <v>6691615</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,50 +1902,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125402537</v>
+        <v>125408185</v>
       </c>
       <c r="B14" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516437</v>
+        <v>516621</v>
       </c>
       <c r="R14" t="n">
-        <v>6691550</v>
+        <v>6691733</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,48 +1999,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125406595</v>
+        <v>125402537</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>56848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516329</v>
+        <v>516437</v>
       </c>
       <c r="R15" t="n">
-        <v>6691615</v>
+        <v>6691550</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -2596,48 +2596,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>56848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R21" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,53 +2698,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B22" t="n">
-        <v>56848</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R22" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125899057</v>
       </c>
       <c r="B3" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>125404325</v>
       </c>
       <c r="B4" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125402480</v>
+        <v>125402947</v>
       </c>
       <c r="B5" t="n">
-        <v>56848</v>
+        <v>97242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,42 +1010,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516445</v>
+        <v>516437</v>
       </c>
       <c r="R5" t="n">
-        <v>6691532</v>
+        <v>6691535</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125402947</v>
+        <v>125402480</v>
       </c>
       <c r="B6" t="n">
-        <v>97233</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,37 +1107,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516437</v>
+        <v>516445</v>
       </c>
       <c r="R6" t="n">
-        <v>6691535</v>
+        <v>6691532</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>125404723</v>
       </c>
       <c r="B7" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>125406131</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,53 +1407,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B9" t="n">
-        <v>56839</v>
+        <v>98382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R9" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,48 +1504,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B10" t="n">
-        <v>98373</v>
+        <v>56840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R10" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>125407168</v>
       </c>
       <c r="B11" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>125406787</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125406595</v>
+        <v>125408185</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516329</v>
+        <v>516621</v>
       </c>
       <c r="R13" t="n">
-        <v>6691615</v>
+        <v>6691733</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,45 +1902,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408185</v>
+        <v>125402537</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>56849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516621</v>
+        <v>516437</v>
       </c>
       <c r="R14" t="n">
-        <v>6691733</v>
+        <v>6691550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,53 +2004,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125402537</v>
+        <v>125406595</v>
       </c>
       <c r="B15" t="n">
-        <v>56848</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516437</v>
+        <v>516329</v>
       </c>
       <c r="R15" t="n">
-        <v>6691550</v>
+        <v>6691615</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>125401741</v>
       </c>
       <c r="B16" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>125408231</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>125402359</v>
       </c>
       <c r="B19" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>125408367</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,53 +2596,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B21" t="n">
-        <v>56848</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R21" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2698,48 +2693,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>56849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R22" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>125404997</v>
       </c>
       <c r="B23" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>97233</v>
+        <v>56849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,34 +2908,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R24" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>98373</v>
+        <v>97242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3010,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R25" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>56848</v>
+        <v>98382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,39 +3107,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R26" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -1407,48 +1407,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R9" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,53 +1509,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>56840</v>
+        <v>98382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R10" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125408185</v>
+        <v>125406595</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516621</v>
+        <v>516329</v>
       </c>
       <c r="R13" t="n">
-        <v>6691733</v>
+        <v>6691615</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,50 +1902,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125402537</v>
+        <v>125408185</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516437</v>
+        <v>516621</v>
       </c>
       <c r="R14" t="n">
-        <v>6691550</v>
+        <v>6691733</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,48 +1999,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125406595</v>
+        <v>125402537</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516329</v>
+        <v>516437</v>
       </c>
       <c r="R15" t="n">
-        <v>6691615</v>
+        <v>6691550</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2596,48 +2596,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125405426</v>
+        <v>125404419</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516386</v>
+        <v>516440</v>
       </c>
       <c r="R21" t="n">
-        <v>6691468</v>
+        <v>6691418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,53 +2698,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125404419</v>
+        <v>125405426</v>
       </c>
       <c r="B22" t="n">
-        <v>56849</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516440</v>
+        <v>516386</v>
       </c>
       <c r="R22" t="n">
-        <v>6691418</v>
+        <v>6691468</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125401530</v>
+        <v>125404275</v>
       </c>
       <c r="B24" t="n">
-        <v>56849</v>
+        <v>97242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,39 +2908,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516605</v>
+        <v>516445</v>
       </c>
       <c r="R24" t="n">
-        <v>6691608</v>
+        <v>6691423</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2999,10 +2994,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125404275</v>
+        <v>125406873</v>
       </c>
       <c r="B25" t="n">
-        <v>97242</v>
+        <v>98382</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,21 +3005,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3034,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516445</v>
+        <v>516372</v>
       </c>
       <c r="R25" t="n">
-        <v>6691423</v>
+        <v>6691600</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,10 +3091,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125406873</v>
+        <v>125401530</v>
       </c>
       <c r="B26" t="n">
-        <v>98382</v>
+        <v>56849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,34 +3102,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516372</v>
+        <v>516605</v>
       </c>
       <c r="R26" t="n">
-        <v>6691600</v>
+        <v>6691608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -1407,53 +1407,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>98382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R9" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,48 +1504,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B10" t="n">
-        <v>98382</v>
+        <v>56840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R10" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125406595</v>
+        <v>125408185</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516329</v>
+        <v>516621</v>
       </c>
       <c r="R13" t="n">
-        <v>6691615</v>
+        <v>6691733</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,45 +1902,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125408185</v>
+        <v>125402537</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516621</v>
+        <v>516437</v>
       </c>
       <c r="R14" t="n">
-        <v>6691733</v>
+        <v>6691550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,53 +2004,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125402537</v>
+        <v>125406595</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516437</v>
+        <v>516329</v>
       </c>
       <c r="R15" t="n">
-        <v>6691550</v>
+        <v>6691615</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125404275</v>
+        <v>125401530</v>
       </c>
       <c r="B24" t="n">
-        <v>97242</v>
+        <v>56849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,34 +2908,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R24" t="n">
-        <v>6691423</v>
+        <v>6691608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125406873</v>
+        <v>125404275</v>
       </c>
       <c r="B25" t="n">
-        <v>98382</v>
+        <v>97242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3005,21 +3010,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516372</v>
+        <v>516445</v>
       </c>
       <c r="R25" t="n">
-        <v>6691600</v>
+        <v>6691423</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125401530</v>
+        <v>125406873</v>
       </c>
       <c r="B26" t="n">
-        <v>56849</v>
+        <v>98382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3102,39 +3107,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516605</v>
+        <v>516372</v>
       </c>
       <c r="R26" t="n">
-        <v>6691608</v>
+        <v>6691600</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -897,53 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125404325</v>
+        <v>125402947</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>97242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516444</v>
+        <v>516437</v>
       </c>
       <c r="R4" t="n">
-        <v>6691419</v>
+        <v>6691535</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,48 +994,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125402947</v>
+        <v>125404325</v>
       </c>
       <c r="B5" t="n">
-        <v>97242</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516437</v>
+        <v>516444</v>
       </c>
       <c r="R5" t="n">
-        <v>6691535</v>
+        <v>6691419</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1407,48 +1407,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R9" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,53 +1509,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>56840</v>
+        <v>98382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R10" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1902,53 +1902,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125402537</v>
+        <v>125406595</v>
       </c>
       <c r="B14" t="n">
-        <v>56849</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516437</v>
+        <v>516329</v>
       </c>
       <c r="R14" t="n">
-        <v>6691550</v>
+        <v>6691615</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2004,48 +1999,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125406595</v>
+        <v>125402537</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516329</v>
+        <v>516437</v>
       </c>
       <c r="R15" t="n">
-        <v>6691615</v>
+        <v>6691550</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -897,48 +897,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125402947</v>
+        <v>125404325</v>
       </c>
       <c r="B4" t="n">
-        <v>97242</v>
+        <v>57654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516437</v>
+        <v>516444</v>
       </c>
       <c r="R4" t="n">
-        <v>6691535</v>
+        <v>6691419</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,53 +999,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125404325</v>
+        <v>125402947</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>97242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516444</v>
+        <v>516437</v>
       </c>
       <c r="R5" t="n">
-        <v>6691419</v>
+        <v>6691535</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1407,53 +1407,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>98382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R9" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,48 +1504,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B10" t="n">
-        <v>98382</v>
+        <v>56840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R10" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -897,53 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125404325</v>
+        <v>125402947</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>97242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516444</v>
+        <v>516437</v>
       </c>
       <c r="R4" t="n">
-        <v>6691419</v>
+        <v>6691535</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,48 +994,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125402947</v>
+        <v>125404325</v>
       </c>
       <c r="B5" t="n">
-        <v>97242</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516437</v>
+        <v>516444</v>
       </c>
       <c r="R5" t="n">
-        <v>6691535</v>
+        <v>6691419</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1407,48 +1407,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401494</v>
+        <v>125404849</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516605</v>
+        <v>516345</v>
       </c>
       <c r="R9" t="n">
-        <v>6691608</v>
+        <v>6691330</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,53 +1509,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125404849</v>
+        <v>125401494</v>
       </c>
       <c r="B10" t="n">
-        <v>56840</v>
+        <v>98382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516345</v>
+        <v>516605</v>
       </c>
       <c r="R10" t="n">
-        <v>6691330</v>
+        <v>6691608</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116311885</v>
+        <v>112987921</v>
       </c>
       <c r="B2" t="n">
-        <v>97675</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kurlberget (Kurlberget), Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516567</v>
+        <v>516235</v>
       </c>
       <c r="R2" t="n">
-        <v>6691626</v>
+        <v>6691543</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,56 +773,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125899057</v>
+        <v>112987730</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kurlberget Väster, Dlr</t>
+          <t>Ramptjärnen, Ramptjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516357</v>
+        <v>516296</v>
       </c>
       <c r="R3" t="n">
-        <v>6691373</v>
+        <v>6691610</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,27 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Under äldre tall på myrstacken under trädet.</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,44 +859,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Kjell-Åke Gustavsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125402947</v>
+        <v>125408185</v>
       </c>
       <c r="B4" t="n">
-        <v>97242</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,13 +906,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516437</v>
+        <v>516621</v>
       </c>
       <c r="R4" t="n">
-        <v>6691535</v>
+        <v>6691733</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,50 +968,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125404325</v>
+        <v>125408231</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kurlberget, Kurlberget, Dlr</t>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516444</v>
+        <v>516621</v>
       </c>
       <c r="R5" t="n">
-        <v>6691419</v>
+        <v>6691736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,50 +1065,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125402480</v>
+        <v>125408367</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516445</v>
+        <v>516605</v>
       </c>
       <c r="R6" t="n">
-        <v>6691532</v>
+        <v>6691759</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1162,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125404723</v>
+        <v>125404325</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,47 +1173,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516359</v>
+        <v>516444</v>
       </c>
       <c r="R7" t="n">
-        <v>6691288</v>
+        <v>6691419</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,11 +1238,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1264,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125406131</v>
+        <v>67853338</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,37 +1275,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hopsveden (23) V Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516270</v>
+        <v>516463</v>
       </c>
       <c r="R8" t="n">
-        <v>6691537</v>
+        <v>6691461</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1375,12 +1332,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tjädertall mindre hällmark.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,50 +1367,55 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Lars-Erik Nilsson, Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125404849</v>
+        <v>112987856</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1447,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516345</v>
+        <v>516261</v>
       </c>
       <c r="R9" t="n">
-        <v>6691330</v>
+        <v>6691561</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1477,12 +1454,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjädrar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401494</v>
+        <v>112988027</v>
       </c>
       <c r="B10" t="n">
-        <v>98382</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,37 +1502,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516605</v>
+        <v>516183</v>
       </c>
       <c r="R10" t="n">
-        <v>6691608</v>
+        <v>6691512</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,12 +1562,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125407168</v>
+        <v>125401530</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516431</v>
+        <v>516605</v>
       </c>
       <c r="R11" t="n">
-        <v>6691633</v>
+        <v>6691608</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125406787</v>
+        <v>125401741</v>
       </c>
       <c r="B12" t="n">
-        <v>98278</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1719,34 +1712,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516368</v>
+        <v>516551</v>
       </c>
       <c r="R12" t="n">
-        <v>6691594</v>
+        <v>6691659</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,48 +1803,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125408185</v>
+        <v>125402359</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516621</v>
+        <v>516433</v>
       </c>
       <c r="R13" t="n">
-        <v>6691733</v>
+        <v>6691624</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,48 +1905,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125406595</v>
+        <v>125402480</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516329</v>
+        <v>516445</v>
       </c>
       <c r="R14" t="n">
-        <v>6691615</v>
+        <v>6691532</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2002,7 +2010,7 @@
         <v>125402537</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125401741</v>
+        <v>125404419</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,22 +2140,22 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516551</v>
+        <v>516440</v>
       </c>
       <c r="R16" t="n">
-        <v>6691659</v>
+        <v>6691418</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2203,48 +2211,58 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125408231</v>
+        <v>125404723</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516621</v>
+        <v>516359</v>
       </c>
       <c r="R17" t="n">
-        <v>6691736</v>
+        <v>6691288</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2274,6 +2292,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2300,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125404817</v>
+        <v>125404997</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,37 +2334,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516346</v>
+        <v>516353</v>
       </c>
       <c r="R18" t="n">
-        <v>6691330</v>
+        <v>6691382</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125402359</v>
+        <v>125407168</v>
       </c>
       <c r="B19" t="n">
-        <v>56849</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,13 +2465,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>516433</v>
+        <v>516431</v>
       </c>
       <c r="R19" t="n">
-        <v>6691624</v>
+        <v>6691633</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2499,48 +2527,56 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125408367</v>
+        <v>125899057</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516605</v>
+        <v>516357</v>
       </c>
       <c r="R20" t="n">
-        <v>6691759</v>
+        <v>6691373</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2564,12 +2600,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Under äldre tall på myrstacken under trädet.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2584,22 +2635,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson, Kjell-Åke Gustavsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125404419</v>
+        <v>125404849</v>
       </c>
       <c r="B21" t="n">
-        <v>56849</v>
+        <v>57132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2636,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516440</v>
+        <v>516345</v>
       </c>
       <c r="R21" t="n">
-        <v>6691418</v>
+        <v>6691330</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2698,45 +2749,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125405426</v>
+        <v>125404817</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516386</v>
+        <v>516346</v>
       </c>
       <c r="R22" t="n">
-        <v>6691468</v>
+        <v>6691330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125404997</v>
+        <v>112987970</v>
       </c>
       <c r="B23" t="n">
-        <v>56849</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2806,39 +2857,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516353</v>
+        <v>516235</v>
       </c>
       <c r="R23" t="n">
-        <v>6691382</v>
+        <v>6691543</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2865,12 +2912,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2897,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125401530</v>
+        <v>116311885</v>
       </c>
       <c r="B24" t="n">
-        <v>56849</v>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,42 +2955,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+          <t>Kurlberget, Kurlberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516605</v>
+        <v>516567</v>
       </c>
       <c r="R24" t="n">
-        <v>6691608</v>
+        <v>6691626</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2967,12 +3009,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2999,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125404275</v>
+        <v>125401346</v>
       </c>
       <c r="B25" t="n">
-        <v>97242</v>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,21 +3052,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221946</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3034,13 +3076,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516445</v>
+        <v>516657</v>
       </c>
       <c r="R25" t="n">
-        <v>6691423</v>
+        <v>6691643</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3096,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125406873</v>
+        <v>125406131</v>
       </c>
       <c r="B26" t="n">
-        <v>98382</v>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3131,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516372</v>
+        <v>516270</v>
       </c>
       <c r="R26" t="n">
-        <v>6691600</v>
+        <v>6691537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,6 +3232,787 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125406787</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>516368</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6691594</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125405426</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>516386</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6691468</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125406595</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>516329</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6691615</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125402947</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>516437</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6691535</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125404275</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>516445</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6691423</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125401330</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>516659</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6691644</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125401494</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>516605</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6691608</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125406873</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kurlberget/Ramptjärn, Kurlberget/Ramptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>516372</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6691600</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22907-2025 artfynd.xlsx
+++ b/artfynd/A 22907-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987921</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125408185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1062,6 +1082,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125408231</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1184,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125408367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1261,6 +1291,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125404325</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67853338</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987856</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112988027</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125401530</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1800,6 +1855,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125401741</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,6 +1962,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125402359</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2004,6 +2069,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125402480</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,6 +2176,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125402537</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125404419</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,6 +2400,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125404723</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125404997</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125407168</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2644,6 +2739,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125899057</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2746,6 +2846,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125404849</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2843,6 +2948,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125404817</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112987970</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3038,6 +3153,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116311885</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3135,6 +3255,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125401346</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3232,6 +3357,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406131</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3329,6 +3459,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406787</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125405426</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3523,6 +3663,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406595</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3620,6 +3765,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125402947</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3717,6 +3867,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125404275</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3819,6 +3974,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125401330</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3916,6 +4076,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125401494</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4013,8 +4178,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406873</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>